--- a/public/정산기본양식.xlsx
+++ b/public/정산기본양식.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JS\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\ecogreen-tm-ver3\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{325BF20C-0CB0-40A7-BCC3-9FA348E1FF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48CECD8-E5FD-4C26-8869-4DD3CB569FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AD2E0A4F-9FEE-4AB8-8DB9-65C2032D5FD9}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
-    <externalReference r:id="rId6"/>
   </externalReferences>
   <definedNames>
     <definedName name="_Fill" hidden="1">#REF!</definedName>
@@ -28,7 +27,7 @@
     <definedName name="_Key2" hidden="1">#REF!</definedName>
     <definedName name="_Order1" hidden="1">0</definedName>
     <definedName name="_Order2" hidden="1">0</definedName>
-    <definedName name="_Sort" hidden="1">[2]내역서!#REF!</definedName>
+    <definedName name="_Sort" hidden="1">[1]내역서!#REF!</definedName>
     <definedName name="Access_Button" hidden="1">"종합사번1999년_99년02월_퇴사__List"</definedName>
     <definedName name="AccessDatabase" hidden="1">"C:\My Documents\사번\종합사번1999년.mdb"</definedName>
     <definedName name="HTML_CodePage" hidden="1">949</definedName>
@@ -52,28 +51,28 @@
     <definedName name="감가" hidden="1">{"'2분기예산별'!$B$2:$O$38"}</definedName>
     <definedName name="감가3" hidden="1">{"'2분기예산별'!$B$2:$O$38"}</definedName>
     <definedName name="건비" hidden="1">{"'2분기예산별'!$B$2:$O$38"}</definedName>
-    <definedName name="견적서" hidden="1">[3]내역서!#REF!</definedName>
-    <definedName name="ㄴ" hidden="1">[4]내역서!#REF!</definedName>
-    <definedName name="ㄴㄴ" hidden="1">[4]내역서!#REF!</definedName>
-    <definedName name="ㄴㅁㅇㄹ" hidden="1">[5]내역서!#REF!</definedName>
+    <definedName name="견적서" hidden="1">[2]내역서!#REF!</definedName>
+    <definedName name="ㄴ" hidden="1">[3]내역서!#REF!</definedName>
+    <definedName name="ㄴㄴ" hidden="1">[3]내역서!#REF!</definedName>
+    <definedName name="ㄴㅁㅇㄹ" hidden="1">[4]내역서!#REF!</definedName>
     <definedName name="ㄹ" hidden="1">{"'2분기예산별'!$B$2:$O$38"}</definedName>
-    <definedName name="ㅀ" hidden="1">[4]내역서!#REF!</definedName>
+    <definedName name="ㅀ" hidden="1">[3]내역서!#REF!</definedName>
     <definedName name="ㅁㄴㅇ" hidden="1">{#N/A,#N/A,FALSE,"이력서&amp;자기소개서"}</definedName>
     <definedName name="미화" hidden="1">{#N/A,#N/A,FALSE,"이력서&amp;자기소개서"}</definedName>
     <definedName name="미화2" hidden="1">{#N/A,#N/A,FALSE,"이력서&amp;자기소개서"}</definedName>
-    <definedName name="산출" hidden="1">[4]내역서!#REF!</definedName>
-    <definedName name="ㅇㅇ" hidden="1">[4]내역서!#REF!</definedName>
+    <definedName name="산출" hidden="1">[3]내역서!#REF!</definedName>
+    <definedName name="ㅇㅇ" hidden="1">[3]내역서!#REF!</definedName>
     <definedName name="앙" hidden="1">{#N/A,#N/A,FALSE,"이력서&amp;자기소개서"}</definedName>
-    <definedName name="이" hidden="1">[4]내역서!#REF!</definedName>
+    <definedName name="이" hidden="1">[3]내역서!#REF!</definedName>
     <definedName name="인건비" hidden="1">{"'2분기예산별'!$B$2:$O$38"}</definedName>
     <definedName name="인건비1" hidden="1">{"'2분기예산별'!$B$2:$O$38"}</definedName>
-    <definedName name="인건비내역" hidden="1">[3]내역서!#REF!</definedName>
+    <definedName name="인건비내역" hidden="1">[2]내역서!#REF!</definedName>
     <definedName name="직접인건비A" hidden="1">{"'2분기예산별'!$B$2:$O$38"}</definedName>
     <definedName name="직접인건비세부내역A" hidden="1">{"'2분기예산별'!$B$2:$O$38"}</definedName>
-    <definedName name="청구04" hidden="1">[2]내역서!#REF!</definedName>
-    <definedName name="청구4" hidden="1">[4]내역서!#REF!</definedName>
+    <definedName name="청구04" hidden="1">[1]내역서!#REF!</definedName>
+    <definedName name="청구4" hidden="1">[3]내역서!#REF!</definedName>
     <definedName name="총괄표" hidden="1">{"'2분기예산별'!$B$2:$O$38"}</definedName>
-    <definedName name="ㅌ" hidden="1">[5]내역서!#REF!</definedName>
+    <definedName name="ㅌ" hidden="1">[4]내역서!#REF!</definedName>
     <definedName name="ㅏㅏ" hidden="1">{#N/A,#N/A,FALSE,"이력서&amp;자기소개서"}</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -98,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
   <si>
     <t>당월 청구금액</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -207,10 +206,6 @@
   <si>
     <t>안산고잔5차푸르지오-10명</t>
     <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026년 03월 (경비) 정산내역서</t>
-    <phoneticPr fontId="23" type="noConversion"/>
   </si>
   <si>
     <t>주식회사 에코그린티엠  대표이사 </t>
@@ -1353,479 +1348,479 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="4" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="4" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="3" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="3" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="3" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="4" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="3" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="3" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="3" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="3" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="3" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="4" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="3" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="5" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="24" fillId="5" borderId="43" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="24" fillId="5" borderId="43" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="24" fillId="5" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="22" fillId="5" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="30" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="30" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="30" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="30" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="30" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="30" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="30" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="30" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="30" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="30" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="30" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="30" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="33" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="31" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="31" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="32" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="2" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="2" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="3" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="3" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="177" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="3" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="3" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="2" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="2" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="4" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="4" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="3" borderId="39" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="3" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="3" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="4" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="20" fillId="3" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="3" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="3" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="3" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="3" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="41" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="19" fillId="4" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="3" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="5" borderId="42" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="24" fillId="5" borderId="43" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="24" fillId="5" borderId="43" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="24" fillId="5" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="22" fillId="5" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="31" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="31" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="32" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="31" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="33" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="30" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="30" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="30" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="30" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="30" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="30" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="30" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="30" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="30" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="30" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="30" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="30" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1989,201 +1984,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="재활용비용26.03"/>
-      <sheetName val="급여대장26.03"/>
-      <sheetName val="청구26.03"/>
-      <sheetName val="청구X연차퇴직금-나영조26.02"/>
-      <sheetName val="재활용비용26.02"/>
-      <sheetName val="급여대장26.02"/>
-      <sheetName val="청구26.02"/>
-      <sheetName val="재활용비용26.01"/>
-      <sheetName val="급여대장26.01"/>
-      <sheetName val="청구26.01"/>
-      <sheetName val="2026_재활용 5만원"/>
-      <sheetName val="대근청구26.01-전달완료"/>
-      <sheetName val="연차-강행원외3명25.12"/>
-      <sheetName val="연차퇴직금-임웅빈25.12"/>
-      <sheetName val="재활용비용25.12"/>
-      <sheetName val="급여대장25.12"/>
-      <sheetName val="청구25.12"/>
-      <sheetName val="재활용비용25.11"/>
-      <sheetName val="급여대장25.11"/>
-      <sheetName val="청구25.11"/>
-      <sheetName val="대근청구25.10"/>
-      <sheetName val="퇴직금-송순규25.10"/>
-      <sheetName val="재활용비용25.10"/>
-      <sheetName val="급여대장25.10"/>
-      <sheetName val="청구25.10"/>
-      <sheetName val="재활용비용25.09"/>
-      <sheetName val="급여대장25.09"/>
-      <sheetName val="청구25.09"/>
-      <sheetName val="연차퇴직금-조남정25.08"/>
-      <sheetName val="재활용비용25.08"/>
-      <sheetName val="급여대장25.08"/>
-      <sheetName val="청구25.08"/>
-      <sheetName val="재활용비용25.07"/>
-      <sheetName val="급여대장25.07"/>
-      <sheetName val="청구25.07"/>
-      <sheetName val="대근청구25.06"/>
-      <sheetName val="급여대장25.06"/>
-      <sheetName val="재활용비용25.06"/>
-      <sheetName val="청구25.06"/>
-      <sheetName val="재활용비용25.05"/>
-      <sheetName val="급여대장25.05"/>
-      <sheetName val="청구25.05"/>
-      <sheetName val="재활용비용25.04"/>
-      <sheetName val="급여대장25.04"/>
-      <sheetName val="청구25.04"/>
-      <sheetName val="재활용비용25.03"/>
-      <sheetName val="급여대장25.03"/>
-      <sheetName val="청구25.03"/>
-      <sheetName val="재활용비용25.02"/>
-      <sheetName val="급여대장25.02"/>
-      <sheetName val="청구25.02"/>
-      <sheetName val="재활용비용25.01"/>
-      <sheetName val="급여대장25.01"/>
-      <sheetName val="청구25.01"/>
-      <sheetName val="2025 "/>
-      <sheetName val="재활용비용24.12"/>
-      <sheetName val="급여대장24.12"/>
-      <sheetName val="청구24.12"/>
-      <sheetName val="재활용비용24.11"/>
-      <sheetName val="급여대장24.11"/>
-      <sheetName val="청구24.11"/>
-      <sheetName val="재활용비용24.10"/>
-      <sheetName val="급여대장24.10"/>
-      <sheetName val="청구24.10"/>
-      <sheetName val="재활용비용24.09"/>
-      <sheetName val="급여대장24.09"/>
-      <sheetName val="청구24.09"/>
-      <sheetName val="재활용비용24.08"/>
-      <sheetName val="급여대장24.08"/>
-      <sheetName val="청구24.08"/>
-      <sheetName val="재활용비용24.07"/>
-      <sheetName val="급여대장24.07"/>
-      <sheetName val="청구24.07"/>
-      <sheetName val="재활용비용24.06"/>
-      <sheetName val="급여대장24.06"/>
-      <sheetName val="청구24.06"/>
-      <sheetName val="재활용비용24.05"/>
-      <sheetName val="급여대장24.05"/>
-      <sheetName val="청구24.05"/>
-      <sheetName val="재활용비용24.04"/>
-      <sheetName val="급여대장24.04"/>
-      <sheetName val="청구24.04"/>
-      <sheetName val="재활용비용24.03"/>
-      <sheetName val="급여대장24.03"/>
-      <sheetName val="청구24.03"/>
-      <sheetName val="재활용비용24.02"/>
-      <sheetName val="급여대장24.02"/>
-      <sheetName val="청구24.02"/>
-      <sheetName val="재활용비용24.01"/>
-      <sheetName val="급여대장24.01"/>
-      <sheetName val="청구24.01"/>
-      <sheetName val="2024 산출내역"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41"/>
-      <sheetData sheetId="42"/>
-      <sheetData sheetId="43"/>
-      <sheetData sheetId="44"/>
-      <sheetData sheetId="45"/>
-      <sheetData sheetId="46"/>
-      <sheetData sheetId="47"/>
-      <sheetData sheetId="48"/>
-      <sheetData sheetId="49"/>
-      <sheetData sheetId="50"/>
-      <sheetData sheetId="51"/>
-      <sheetData sheetId="52"/>
-      <sheetData sheetId="53"/>
-      <sheetData sheetId="54"/>
-      <sheetData sheetId="55"/>
-      <sheetData sheetId="56"/>
-      <sheetData sheetId="57"/>
-      <sheetData sheetId="58"/>
-      <sheetData sheetId="59"/>
-      <sheetData sheetId="60"/>
-      <sheetData sheetId="61"/>
-      <sheetData sheetId="62"/>
-      <sheetData sheetId="63"/>
-      <sheetData sheetId="64"/>
-      <sheetData sheetId="65"/>
-      <sheetData sheetId="66"/>
-      <sheetData sheetId="67"/>
-      <sheetData sheetId="68"/>
-      <sheetData sheetId="69"/>
-      <sheetData sheetId="70"/>
-      <sheetData sheetId="71"/>
-      <sheetData sheetId="72"/>
-      <sheetData sheetId="73"/>
-      <sheetData sheetId="74"/>
-      <sheetData sheetId="75"/>
-      <sheetData sheetId="76"/>
-      <sheetData sheetId="77"/>
-      <sheetData sheetId="78"/>
-      <sheetData sheetId="79"/>
-      <sheetData sheetId="80"/>
-      <sheetData sheetId="81"/>
-      <sheetData sheetId="82"/>
-      <sheetData sheetId="83"/>
-      <sheetData sheetId="84"/>
-      <sheetData sheetId="85"/>
-      <sheetData sheetId="86"/>
-      <sheetData sheetId="87"/>
-      <sheetData sheetId="88"/>
-      <sheetData sheetId="89"/>
-      <sheetData sheetId="90"/>
-      <sheetData sheetId="91"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2684,7 +2484,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2699,7 +2499,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2722,7 +2522,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3093,1134 +2893,1170 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="158"/>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
+      <c r="A1" s="77"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="159"/>
-      <c r="B2" s="159"/>
-      <c r="C2" s="159"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
     </row>
     <row r="3" spans="1:17" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="158"/>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
     </row>
     <row r="4" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="157" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="157"/>
-      <c r="C4" s="157"/>
-      <c r="D4" s="157"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="157"/>
-      <c r="G4" s="157"/>
-      <c r="H4" s="157"/>
-      <c r="I4" s="157"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="157"/>
-      <c r="L4" s="157"/>
-      <c r="M4" s="157"/>
-      <c r="N4" s="157"/>
-      <c r="O4" s="157"/>
-      <c r="P4" s="157"/>
-      <c r="Q4" s="157"/>
+      <c r="A4" s="79" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="79"/>
+      <c r="L4" s="79"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="79"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="79"/>
+      <c r="Q4" s="79"/>
     </row>
     <row r="5" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="155" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="155"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="155"/>
-      <c r="K5" s="155"/>
-      <c r="L5" s="155"/>
-      <c r="M5" s="155"/>
-      <c r="N5" s="155"/>
-      <c r="O5" s="155"/>
-      <c r="P5" s="155"/>
-      <c r="Q5" s="155"/>
+      <c r="A5" s="80" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="80"/>
+      <c r="L5" s="80"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="80"/>
+      <c r="O5" s="80"/>
+      <c r="P5" s="80"/>
+      <c r="Q5" s="80"/>
     </row>
     <row r="6" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="155" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="155"/>
-      <c r="C6" s="155"/>
-      <c r="D6" s="155"/>
-      <c r="E6" s="155"/>
-      <c r="F6" s="155"/>
-      <c r="G6" s="155"/>
-      <c r="H6" s="155"/>
-      <c r="I6" s="155"/>
-      <c r="J6" s="155"/>
-      <c r="K6" s="155"/>
-      <c r="L6" s="155"/>
-      <c r="M6" s="155"/>
-      <c r="N6" s="155"/>
-      <c r="O6" s="155"/>
-      <c r="P6" s="155"/>
-      <c r="Q6" s="155"/>
+      <c r="A6" s="80" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
+      <c r="Q6" s="80"/>
     </row>
     <row r="7" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="156" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="156"/>
-      <c r="C7" s="156"/>
-      <c r="D7" s="156"/>
-      <c r="E7" s="156"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="156"/>
-      <c r="H7" s="156"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="156"/>
-      <c r="K7" s="156"/>
-      <c r="L7" s="156"/>
-      <c r="M7" s="156"/>
-      <c r="N7" s="156"/>
-      <c r="O7" s="156"/>
-      <c r="P7" s="156"/>
-      <c r="Q7" s="156"/>
+      <c r="A7" s="81" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="81"/>
+      <c r="O7" s="81"/>
+      <c r="P7" s="81"/>
+      <c r="Q7" s="81"/>
     </row>
     <row r="8" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="155" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="155"/>
-      <c r="C8" s="155"/>
-      <c r="D8" s="155"/>
-      <c r="E8" s="155"/>
-      <c r="F8" s="155"/>
-      <c r="G8" s="155"/>
-      <c r="H8" s="155"/>
-      <c r="I8" s="155"/>
-      <c r="J8" s="155"/>
-      <c r="K8" s="155"/>
-      <c r="L8" s="155"/>
-      <c r="M8" s="155"/>
-      <c r="N8" s="155"/>
-      <c r="O8" s="155"/>
-      <c r="P8" s="155"/>
-      <c r="Q8" s="155"/>
+      <c r="A8" s="80" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="80"/>
+      <c r="L8" s="80"/>
+      <c r="M8" s="80"/>
+      <c r="N8" s="80"/>
+      <c r="O8" s="80"/>
+      <c r="P8" s="80"/>
+      <c r="Q8" s="80"/>
     </row>
     <row r="9" spans="1:17" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:17" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="154"/>
-      <c r="B10" s="154"/>
-      <c r="C10" s="154"/>
-      <c r="D10" s="154"/>
-      <c r="E10" s="154"/>
-      <c r="F10" s="154"/>
-      <c r="G10" s="154"/>
-      <c r="H10" s="154"/>
-      <c r="I10" s="154"/>
-      <c r="J10" s="154"/>
-      <c r="K10" s="154"/>
-      <c r="L10" s="154"/>
-      <c r="M10" s="154"/>
-      <c r="N10" s="154"/>
-      <c r="O10" s="154"/>
-      <c r="P10" s="154"/>
-      <c r="Q10" s="154"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="76"/>
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="76"/>
+      <c r="K10" s="76"/>
+      <c r="L10" s="76"/>
+      <c r="M10" s="76"/>
+      <c r="N10" s="76"/>
+      <c r="O10" s="76"/>
+      <c r="P10" s="76"/>
+      <c r="Q10" s="76"/>
     </row>
     <row r="11" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="153" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="153"/>
-      <c r="C11" s="153"/>
-      <c r="D11" s="153"/>
-      <c r="E11" s="153"/>
-      <c r="F11" s="153"/>
-      <c r="G11" s="153"/>
-      <c r="H11" s="153"/>
-      <c r="I11" s="153"/>
-      <c r="J11" s="153"/>
-      <c r="K11" s="153"/>
-      <c r="L11" s="153"/>
-      <c r="M11" s="153"/>
-      <c r="N11" s="153"/>
-      <c r="O11" s="153"/>
-      <c r="P11" s="153"/>
-      <c r="Q11" s="153"/>
+      <c r="A11" s="82" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="82"/>
+      <c r="J11" s="82"/>
+      <c r="K11" s="82"/>
+      <c r="L11" s="82"/>
+      <c r="M11" s="82"/>
+      <c r="N11" s="82"/>
+      <c r="O11" s="82"/>
+      <c r="P11" s="82"/>
+      <c r="Q11" s="82"/>
     </row>
     <row r="12" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="153" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="153"/>
-      <c r="C12" s="153"/>
-      <c r="D12" s="153"/>
-      <c r="E12" s="153"/>
-      <c r="F12" s="153"/>
-      <c r="G12" s="153"/>
-      <c r="H12" s="153"/>
-      <c r="I12" s="153"/>
-      <c r="J12" s="153"/>
-      <c r="K12" s="153"/>
-      <c r="L12" s="153"/>
-      <c r="M12" s="153"/>
-      <c r="N12" s="153"/>
-      <c r="O12" s="153"/>
-      <c r="P12" s="153"/>
-      <c r="Q12" s="153"/>
+      <c r="A12" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="82"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="82"/>
+      <c r="N12" s="82"/>
+      <c r="O12" s="82"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82"/>
     </row>
     <row r="13" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="152" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="152"/>
-      <c r="C13" s="152"/>
-      <c r="D13" s="152"/>
-      <c r="E13" s="152"/>
-      <c r="F13" s="152"/>
-      <c r="G13" s="152"/>
-      <c r="H13" s="152"/>
-      <c r="I13" s="152"/>
-      <c r="J13" s="152"/>
-      <c r="K13" s="152"/>
-      <c r="L13" s="152"/>
-      <c r="M13" s="152"/>
-      <c r="N13" s="152"/>
-      <c r="O13" s="152"/>
-      <c r="P13" s="152"/>
-      <c r="Q13" s="152"/>
+      <c r="A13" s="83" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="83"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="83"/>
+      <c r="K13" s="83"/>
+      <c r="L13" s="83"/>
+      <c r="M13" s="83"/>
+      <c r="N13" s="83"/>
+      <c r="O13" s="83"/>
+      <c r="P13" s="83"/>
+      <c r="Q13" s="83"/>
     </row>
     <row r="14" spans="1:17" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="126"/>
-      <c r="B14" s="126"/>
-      <c r="C14" s="126"/>
-      <c r="D14" s="126"/>
-      <c r="E14" s="126"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="126"/>
-      <c r="H14" s="126"/>
-      <c r="I14" s="126"/>
-      <c r="J14" s="126"/>
-      <c r="K14" s="126"/>
-      <c r="L14" s="126"/>
-      <c r="M14" s="126"/>
-      <c r="N14" s="126"/>
-      <c r="O14" s="126"/>
-      <c r="P14" s="126"/>
-      <c r="Q14" s="126"/>
+      <c r="A14" s="71"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="71"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="71"/>
+      <c r="N14" s="71"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
     </row>
     <row r="15" spans="1:17" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="151" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="151"/>
-      <c r="D15" s="151"/>
-      <c r="E15" s="113" t="s">
+      <c r="B15" s="84" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="113"/>
-      <c r="G15" s="113"/>
-      <c r="H15" s="113"/>
-      <c r="I15" s="113"/>
-      <c r="J15" s="113" t="s">
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="K15" s="113"/>
-      <c r="L15" s="113"/>
-      <c r="M15" s="113"/>
-      <c r="N15" s="150" t="s">
+      <c r="F15" s="85"/>
+      <c r="G15" s="85"/>
+      <c r="H15" s="85"/>
+      <c r="I15" s="85"/>
+      <c r="J15" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="O15" s="149"/>
-      <c r="P15" s="148"/>
-      <c r="Q15" s="106"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="85"/>
+      <c r="M15" s="85"/>
+      <c r="N15" s="86" t="s">
+        <v>49</v>
+      </c>
+      <c r="O15" s="87"/>
+      <c r="P15" s="88"/>
+      <c r="Q15" s="62"/>
     </row>
     <row r="16" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="147" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="146"/>
-      <c r="D16" s="145"/>
-      <c r="E16" s="119" t="s">
+      <c r="B16" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="119"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="131">
+      <c r="C16" s="90"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="95" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="96">
         <f>O62</f>
         <v>0</v>
       </c>
-      <c r="K16" s="131"/>
-      <c r="L16" s="131"/>
-      <c r="M16" s="131"/>
-      <c r="N16" s="130" t="s">
-        <v>47</v>
-      </c>
-      <c r="O16" s="129"/>
-      <c r="P16" s="128"/>
-      <c r="Q16" s="127"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="96"/>
+      <c r="M16" s="96"/>
+      <c r="N16" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="O16" s="98"/>
+      <c r="P16" s="99"/>
+      <c r="Q16" s="72"/>
     </row>
     <row r="17" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="144"/>
-      <c r="C17" s="143"/>
-      <c r="D17" s="142"/>
-      <c r="E17" s="119" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="119"/>
-      <c r="G17" s="119"/>
-      <c r="H17" s="119"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="131">
+      <c r="B17" s="92"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="95" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="95"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="96">
         <f>O63</f>
         <v>0</v>
       </c>
-      <c r="K17" s="131"/>
-      <c r="L17" s="131"/>
-      <c r="M17" s="131"/>
-      <c r="N17" s="135" t="s">
+      <c r="K17" s="96"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="100" t="s">
+        <v>43</v>
+      </c>
+      <c r="O17" s="101"/>
+      <c r="P17" s="102"/>
+      <c r="Q17" s="62"/>
+    </row>
+    <row r="18" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="92"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="95" t="s">
         <v>44</v>
       </c>
-      <c r="O17" s="134"/>
-      <c r="P17" s="133"/>
-      <c r="Q17" s="106"/>
-    </row>
-    <row r="18" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="144"/>
-      <c r="C18" s="143"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="119" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="119"/>
-      <c r="G18" s="119"/>
-      <c r="H18" s="119"/>
-      <c r="I18" s="119"/>
-      <c r="J18" s="131">
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="96">
         <f>O64</f>
         <v>0</v>
       </c>
-      <c r="K18" s="131"/>
-      <c r="L18" s="131"/>
-      <c r="M18" s="131"/>
-      <c r="N18" s="135" t="s">
-        <v>44</v>
-      </c>
-      <c r="O18" s="134"/>
-      <c r="P18" s="133"/>
-      <c r="Q18" s="106"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96"/>
+      <c r="M18" s="96"/>
+      <c r="N18" s="100" t="s">
+        <v>43</v>
+      </c>
+      <c r="O18" s="101"/>
+      <c r="P18" s="102"/>
+      <c r="Q18" s="62"/>
     </row>
     <row r="19" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="144"/>
-      <c r="C19" s="143"/>
-      <c r="D19" s="142"/>
-      <c r="E19" s="119" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" s="119"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="119"/>
-      <c r="J19" s="131">
+      <c r="B19" s="92"/>
+      <c r="C19" s="93"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="95" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="96">
         <f>O67</f>
         <v>0</v>
       </c>
-      <c r="K19" s="131"/>
-      <c r="L19" s="131"/>
-      <c r="M19" s="131"/>
-      <c r="N19" s="135" t="s">
-        <v>42</v>
-      </c>
-      <c r="O19" s="134"/>
-      <c r="P19" s="133"/>
-      <c r="Q19" s="106"/>
+      <c r="K19" s="96"/>
+      <c r="L19" s="96"/>
+      <c r="M19" s="96"/>
+      <c r="N19" s="100" t="s">
+        <v>41</v>
+      </c>
+      <c r="O19" s="101"/>
+      <c r="P19" s="102"/>
+      <c r="Q19" s="62"/>
     </row>
     <row r="20" spans="1:17" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="141"/>
-      <c r="C20" s="140"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="135" t="str">
+      <c r="B20" s="75"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="100" t="str">
         <f>L68</f>
         <v>공백차감(2일)</v>
       </c>
-      <c r="F20" s="134"/>
-      <c r="G20" s="134"/>
-      <c r="H20" s="134"/>
-      <c r="I20" s="133"/>
-      <c r="J20" s="138">
+      <c r="F20" s="101"/>
+      <c r="G20" s="101"/>
+      <c r="H20" s="101"/>
+      <c r="I20" s="102"/>
+      <c r="J20" s="103">
         <f>O68</f>
         <v>0</v>
       </c>
-      <c r="K20" s="137"/>
-      <c r="L20" s="137"/>
-      <c r="M20" s="136"/>
-      <c r="N20" s="135" t="s">
-        <v>41</v>
-      </c>
-      <c r="O20" s="134"/>
-      <c r="P20" s="133"/>
-      <c r="Q20" s="106"/>
+      <c r="K20" s="104"/>
+      <c r="L20" s="104"/>
+      <c r="M20" s="105"/>
+      <c r="N20" s="100" t="s">
+        <v>40</v>
+      </c>
+      <c r="O20" s="101"/>
+      <c r="P20" s="102"/>
+      <c r="Q20" s="62"/>
     </row>
     <row r="21" spans="1:17" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="132" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="132"/>
-      <c r="D21" s="132"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="132"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="132"/>
-      <c r="J21" s="131">
+      <c r="B21" s="106" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="106"/>
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="96">
         <f>ROUNDDOWN(SUM(J16:M20),-1)</f>
         <v>0</v>
       </c>
-      <c r="K21" s="131"/>
-      <c r="L21" s="131"/>
-      <c r="M21" s="131"/>
-      <c r="N21" s="130"/>
-      <c r="O21" s="129"/>
-      <c r="P21" s="128"/>
-      <c r="Q21" s="127"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="96"/>
+      <c r="M21" s="96"/>
+      <c r="N21" s="97"/>
+      <c r="O21" s="98"/>
+      <c r="P21" s="99"/>
+      <c r="Q21" s="72"/>
     </row>
     <row r="22" spans="1:17" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="123"/>
-      <c r="C22" s="123"/>
-      <c r="D22" s="126"/>
-      <c r="E22" s="126"/>
-      <c r="F22" s="126"/>
-      <c r="G22" s="126"/>
-      <c r="H22" s="126"/>
-      <c r="I22" s="126"/>
-      <c r="J22" s="126"/>
-      <c r="K22" s="126"/>
-      <c r="L22" s="126"/>
-      <c r="M22" s="125"/>
-      <c r="N22" s="125"/>
-      <c r="O22" s="124"/>
-      <c r="P22" s="124"/>
-      <c r="Q22" s="123"/>
-    </row>
-    <row r="23" spans="1:17" s="101" customFormat="1" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="71"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="69"/>
+      <c r="P22" s="69"/>
+      <c r="Q22" s="68"/>
+    </row>
+    <row r="23" spans="1:17" s="57" customFormat="1" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="119" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="119" t="s">
+      <c r="B23" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="G23" s="119"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="120" t="s">
+      <c r="C23" s="95"/>
+      <c r="D23" s="95"/>
+      <c r="E23" s="95"/>
+      <c r="F23" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="J23" s="119" t="s">
+      <c r="G23" s="95"/>
+      <c r="H23" s="95"/>
+      <c r="I23" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="K23" s="119"/>
-      <c r="L23" s="122" t="s">
+      <c r="J23" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="M23" s="122"/>
-      <c r="N23" s="121" t="s">
+      <c r="K23" s="95"/>
+      <c r="L23" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="O23" s="121"/>
-      <c r="P23" s="121"/>
-      <c r="Q23" s="120"/>
+      <c r="M23" s="107"/>
+      <c r="N23" s="108" t="s">
+        <v>33</v>
+      </c>
+      <c r="O23" s="108"/>
+      <c r="P23" s="108"/>
+      <c r="Q23" s="67"/>
     </row>
     <row r="24" spans="1:17" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="119" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="119"/>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="118">
+      <c r="B24" s="95" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="109">
         <v>97677.33</v>
       </c>
-      <c r="G24" s="118"/>
-      <c r="H24" s="118"/>
-      <c r="I24" s="117">
+      <c r="G24" s="109"/>
+      <c r="H24" s="109"/>
+      <c r="I24" s="110">
         <f>J21/F26</f>
         <v>0</v>
       </c>
-      <c r="J24" s="115">
+      <c r="J24" s="111">
         <f>ROUND(F24*I24,-1)</f>
         <v>0</v>
       </c>
-      <c r="K24" s="115"/>
-      <c r="L24" s="116"/>
-      <c r="M24" s="116"/>
-      <c r="N24" s="115">
+      <c r="K24" s="111"/>
+      <c r="L24" s="112"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="111">
         <f>SUM(J24:M24)</f>
         <v>0</v>
       </c>
-      <c r="O24" s="115"/>
-      <c r="P24" s="115"/>
-      <c r="Q24" s="114"/>
+      <c r="O24" s="111"/>
+      <c r="P24" s="111"/>
+      <c r="Q24" s="66"/>
     </row>
     <row r="25" spans="1:17" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="119" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="119"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="118">
+      <c r="B25" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="95"/>
+      <c r="D25" s="95"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="109">
         <v>13915.44</v>
       </c>
-      <c r="G25" s="118"/>
-      <c r="H25" s="118"/>
-      <c r="I25" s="117"/>
-      <c r="J25" s="115">
+      <c r="G25" s="109"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="110"/>
+      <c r="J25" s="111">
         <f>ROUND(F25*I24,-1)</f>
         <v>0</v>
       </c>
-      <c r="K25" s="115"/>
-      <c r="L25" s="116">
+      <c r="K25" s="111"/>
+      <c r="L25" s="112">
         <f>ROUND(J25*10%,-1)</f>
         <v>0</v>
       </c>
-      <c r="M25" s="116"/>
-      <c r="N25" s="115">
+      <c r="M25" s="112"/>
+      <c r="N25" s="111">
         <f>SUM(J25:M25)</f>
         <v>0</v>
       </c>
-      <c r="O25" s="115"/>
-      <c r="P25" s="115"/>
-      <c r="Q25" s="114"/>
-    </row>
-    <row r="26" spans="1:17" s="107" customFormat="1" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="113" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="113"/>
-      <c r="D26" s="113"/>
-      <c r="E26" s="113"/>
-      <c r="F26" s="112">
+      <c r="O25" s="111"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="66"/>
+    </row>
+    <row r="26" spans="1:17" s="63" customFormat="1" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="85" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="85"/>
+      <c r="D26" s="85"/>
+      <c r="E26" s="85"/>
+      <c r="F26" s="113">
         <f>SUM(F24:H25)</f>
         <v>111592.77</v>
       </c>
-      <c r="G26" s="112"/>
-      <c r="H26" s="112"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="109">
+      <c r="G26" s="113"/>
+      <c r="H26" s="113"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="114">
         <f>SUM(J24:K25)</f>
         <v>0</v>
       </c>
-      <c r="K26" s="109"/>
-      <c r="L26" s="110">
+      <c r="K26" s="114"/>
+      <c r="L26" s="115">
         <f>SUM(L24:M25)</f>
         <v>0</v>
       </c>
-      <c r="M26" s="110"/>
-      <c r="N26" s="109">
+      <c r="M26" s="115"/>
+      <c r="N26" s="114">
         <f>SUM(J26:M26)</f>
         <v>0</v>
       </c>
-      <c r="O26" s="109"/>
-      <c r="P26" s="109"/>
-      <c r="Q26" s="108"/>
+      <c r="O26" s="114"/>
+      <c r="P26" s="114"/>
+      <c r="Q26" s="64"/>
     </row>
     <row r="27" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="105" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="106"/>
-      <c r="D27" s="106"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="106"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="106"/>
-      <c r="I27" s="106"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="106"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="106"/>
-      <c r="N27" s="106"/>
-      <c r="O27" s="106"/>
-      <c r="P27" s="106"/>
-      <c r="Q27" s="106"/>
+      <c r="B27" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="62"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="62"/>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="62"/>
     </row>
     <row r="28" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="105" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="106"/>
-      <c r="D28" s="106"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="106"/>
-      <c r="I28" s="106"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="106"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="106"/>
-      <c r="N28" s="106"/>
-      <c r="O28" s="106"/>
-      <c r="P28" s="106"/>
-      <c r="Q28" s="106"/>
+      <c r="B28" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="62"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="62"/>
+      <c r="M28" s="62"/>
+      <c r="N28" s="62"/>
+      <c r="O28" s="62"/>
+      <c r="P28" s="62"/>
+      <c r="Q28" s="62"/>
     </row>
     <row r="29" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="105" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="104"/>
+      <c r="B29" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="60"/>
     </row>
     <row r="30" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="101"/>
-      <c r="B30" s="101"/>
-      <c r="C30" s="101"/>
-      <c r="P30" s="103" t="s">
-        <v>27</v>
+      <c r="A30" s="57"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="57"/>
+      <c r="P30" s="59" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="101"/>
-      <c r="B31" s="101"/>
-      <c r="C31" s="101"/>
+      <c r="A31" s="57"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="57"/>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="101"/>
-      <c r="B32" s="101"/>
-      <c r="C32" s="102"/>
+      <c r="A32" s="57"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="58"/>
     </row>
     <row r="33" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="101"/>
-      <c r="B33" s="101"/>
-      <c r="C33" s="101"/>
+      <c r="A33" s="57"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="57"/>
     </row>
     <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="101"/>
-      <c r="B34" s="101"/>
-      <c r="C34" s="101"/>
+      <c r="A34" s="57"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="57"/>
     </row>
     <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="101"/>
-      <c r="B35" s="101"/>
-      <c r="C35" s="101"/>
+      <c r="A35" s="57"/>
+      <c r="B35" s="57"/>
+      <c r="C35" s="57"/>
     </row>
     <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="101"/>
-      <c r="B36" s="101"/>
-      <c r="C36" s="101"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
     </row>
     <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="101"/>
-      <c r="B37" s="101"/>
-      <c r="C37" s="101"/>
+      <c r="A37" s="57"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
     </row>
     <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="101"/>
-      <c r="B38" s="101"/>
-      <c r="C38" s="101"/>
+      <c r="A38" s="57"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="57"/>
     </row>
     <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="101"/>
-      <c r="B39" s="101"/>
-      <c r="C39" s="101"/>
+      <c r="A39" s="57"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="57"/>
     </row>
     <row r="40" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="101"/>
-      <c r="B40" s="101"/>
-      <c r="C40" s="101"/>
+      <c r="A40" s="57"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
     </row>
     <row r="42" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="100" t="s">
-        <v>26</v>
-      </c>
-      <c r="B42" s="100"/>
-      <c r="C42" s="100"/>
-      <c r="D42" s="100"/>
-      <c r="E42" s="100"/>
-      <c r="F42" s="100"/>
-      <c r="G42" s="100"/>
-      <c r="H42" s="100"/>
-      <c r="I42" s="100"/>
-      <c r="J42" s="100"/>
-      <c r="K42" s="100"/>
-      <c r="L42" s="100"/>
-      <c r="M42" s="100"/>
-      <c r="N42" s="100"/>
-      <c r="O42" s="100"/>
-      <c r="P42" s="100"/>
-      <c r="Q42" s="100"/>
+      <c r="A42" s="116" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" s="116"/>
+      <c r="C42" s="116"/>
+      <c r="D42" s="116"/>
+      <c r="E42" s="116"/>
+      <c r="F42" s="116"/>
+      <c r="G42" s="116"/>
+      <c r="H42" s="116"/>
+      <c r="I42" s="116"/>
+      <c r="J42" s="116"/>
+      <c r="K42" s="116"/>
+      <c r="L42" s="116"/>
+      <c r="M42" s="116"/>
+      <c r="N42" s="116"/>
+      <c r="O42" s="116"/>
+      <c r="P42" s="116"/>
+      <c r="Q42" s="116"/>
     </row>
     <row r="47" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="99" t="s">
-        <v>25</v>
-      </c>
-      <c r="B47" s="99"/>
-      <c r="C47" s="99"/>
-      <c r="D47" s="99"/>
-      <c r="E47" s="99"/>
-      <c r="F47" s="99"/>
-      <c r="G47" s="99"/>
-      <c r="H47" s="99"/>
-      <c r="I47" s="99"/>
-      <c r="J47" s="99"/>
-      <c r="K47" s="99"/>
-      <c r="L47" s="99"/>
-      <c r="M47" s="99"/>
-      <c r="N47" s="99"/>
-      <c r="O47" s="99"/>
-      <c r="P47" s="99"/>
-      <c r="Q47" s="99"/>
+      <c r="A47" s="117"/>
+      <c r="B47" s="117"/>
+      <c r="C47" s="117"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="117"/>
+      <c r="I47" s="117"/>
+      <c r="J47" s="117"/>
+      <c r="K47" s="117"/>
+      <c r="L47" s="117"/>
+      <c r="M47" s="117"/>
+      <c r="N47" s="117"/>
+      <c r="O47" s="117"/>
+      <c r="P47" s="117"/>
+      <c r="Q47" s="117"/>
     </row>
     <row r="48" spans="1:17" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F48" s="98"/>
-      <c r="G48" s="98"/>
-      <c r="H48" s="98"/>
-      <c r="I48" s="98"/>
-      <c r="K48" s="97"/>
-      <c r="L48" s="97"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="56"/>
+      <c r="H48" s="56"/>
+      <c r="I48" s="56"/>
+      <c r="K48" s="55"/>
+      <c r="L48" s="55"/>
     </row>
     <row r="49" spans="2:16" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F49" s="98"/>
-      <c r="G49" s="98"/>
-      <c r="H49" s="98"/>
-      <c r="I49" s="98"/>
-      <c r="K49" s="97"/>
-      <c r="L49" s="97"/>
-      <c r="M49" s="97"/>
-      <c r="N49" s="96" t="s">
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="56"/>
+      <c r="K49" s="55"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="55"/>
+      <c r="N49" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="O49" s="95"/>
-      <c r="P49" s="94"/>
-    </row>
-    <row r="50" spans="2:16" s="84" customFormat="1" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="93" t="s">
+      <c r="O49" s="119"/>
+      <c r="P49" s="120"/>
+    </row>
+    <row r="50" spans="2:16" s="45" customFormat="1" ht="47.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="C50" s="90" t="s">
+      <c r="C50" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D50" s="92" t="s">
+      <c r="D50" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="E50" s="91" t="s">
+      <c r="E50" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="F50" s="90" t="s">
+      <c r="F50" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="G50" s="90" t="s">
+      <c r="G50" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="H50" s="90" t="s">
+      <c r="H50" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I50" s="89" t="s">
+      <c r="I50" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="J50" s="88" t="s">
+      <c r="J50" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="K50" s="86" t="s">
+      <c r="K50" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="L50" s="86" t="s">
+      <c r="L50" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="M50" s="87" t="s">
+      <c r="M50" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="N50" s="87" t="s">
+      <c r="N50" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="O50" s="86" t="s">
+      <c r="O50" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="P50" s="85" t="s">
+      <c r="P50" s="46" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="51" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="68"/>
-      <c r="C51" s="76"/>
-      <c r="D51" s="76"/>
-      <c r="E51" s="76"/>
-      <c r="F51" s="80"/>
-      <c r="G51" s="83"/>
-      <c r="H51" s="62"/>
-      <c r="I51" s="61"/>
-      <c r="J51" s="82"/>
-      <c r="K51" s="59"/>
-      <c r="L51" s="59"/>
-      <c r="M51" s="59"/>
-      <c r="N51" s="57"/>
-      <c r="O51" s="57"/>
-      <c r="P51" s="81"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="23"/>
+      <c r="I51" s="22"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+      <c r="M51" s="20"/>
+      <c r="N51" s="18"/>
+      <c r="O51" s="18"/>
+      <c r="P51" s="42"/>
     </row>
     <row r="52" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="68"/>
-      <c r="C52" s="65"/>
-      <c r="D52" s="65"/>
-      <c r="E52" s="65"/>
-      <c r="F52" s="80"/>
-      <c r="G52" s="79"/>
-      <c r="H52" s="62"/>
-      <c r="I52" s="61"/>
-      <c r="J52" s="60"/>
-      <c r="K52" s="59"/>
-      <c r="L52" s="59"/>
-      <c r="M52" s="69"/>
-      <c r="N52" s="57"/>
-      <c r="O52" s="57"/>
-      <c r="P52" s="56"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
+      <c r="P52" s="17"/>
     </row>
     <row r="53" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="68"/>
-      <c r="C53" s="65"/>
-      <c r="D53" s="66"/>
-      <c r="E53" s="65"/>
-      <c r="F53" s="80"/>
-      <c r="G53" s="79"/>
-      <c r="H53" s="62"/>
-      <c r="I53" s="61"/>
-      <c r="J53" s="60"/>
-      <c r="K53" s="59"/>
-      <c r="L53" s="59"/>
-      <c r="M53" s="69"/>
-      <c r="N53" s="57"/>
-      <c r="O53" s="57"/>
-      <c r="P53" s="56"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="23"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="21"/>
+      <c r="K53" s="20"/>
+      <c r="L53" s="20"/>
+      <c r="M53" s="30"/>
+      <c r="N53" s="18"/>
+      <c r="O53" s="18"/>
+      <c r="P53" s="17"/>
     </row>
     <row r="54" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="68"/>
-      <c r="C54" s="67"/>
-      <c r="D54" s="66"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="64"/>
-      <c r="G54" s="79"/>
-      <c r="H54" s="73"/>
-      <c r="I54" s="72"/>
-      <c r="J54" s="60"/>
-      <c r="K54" s="59"/>
-      <c r="L54" s="59"/>
-      <c r="M54" s="69"/>
-      <c r="N54" s="57"/>
-      <c r="O54" s="57"/>
-      <c r="P54" s="56"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="33"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="20"/>
+      <c r="L54" s="20"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="18"/>
+      <c r="P54" s="17"/>
     </row>
     <row r="55" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="68"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="78"/>
-      <c r="E55" s="65"/>
-      <c r="F55" s="75"/>
-      <c r="G55" s="63"/>
-      <c r="H55" s="62"/>
-      <c r="I55" s="61"/>
-      <c r="J55" s="60"/>
-      <c r="K55" s="59"/>
-      <c r="L55" s="59"/>
-      <c r="M55" s="69"/>
-      <c r="N55" s="57"/>
-      <c r="O55" s="57"/>
-      <c r="P55" s="56"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="39"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="23"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="21"/>
+      <c r="K55" s="20"/>
+      <c r="L55" s="20"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="18"/>
+      <c r="P55" s="17"/>
     </row>
     <row r="56" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="68"/>
-      <c r="C56" s="77"/>
-      <c r="D56" s="66"/>
-      <c r="E56" s="76"/>
-      <c r="F56" s="75"/>
-      <c r="G56" s="70"/>
-      <c r="H56" s="73"/>
-      <c r="I56" s="72"/>
-      <c r="J56" s="60"/>
-      <c r="K56" s="59"/>
-      <c r="L56" s="59"/>
-      <c r="M56" s="58"/>
-      <c r="N56" s="57"/>
-      <c r="O56" s="57"/>
-      <c r="P56" s="56"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="34"/>
+      <c r="I56" s="33"/>
+      <c r="J56" s="21"/>
+      <c r="K56" s="20"/>
+      <c r="L56" s="20"/>
+      <c r="M56" s="19"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
+      <c r="P56" s="17"/>
     </row>
     <row r="57" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="68"/>
-      <c r="C57" s="67"/>
-      <c r="D57" s="66"/>
-      <c r="E57" s="67"/>
-      <c r="F57" s="71"/>
-      <c r="G57" s="74"/>
-      <c r="H57" s="73"/>
-      <c r="I57" s="72"/>
-      <c r="J57" s="60"/>
-      <c r="K57" s="59"/>
-      <c r="L57" s="59"/>
-      <c r="M57" s="69"/>
-      <c r="N57" s="57"/>
-      <c r="O57" s="57"/>
-      <c r="P57" s="56"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="34"/>
+      <c r="I57" s="33"/>
+      <c r="J57" s="21"/>
+      <c r="K57" s="20"/>
+      <c r="L57" s="20"/>
+      <c r="M57" s="30"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="18"/>
+      <c r="P57" s="17"/>
     </row>
     <row r="58" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="68"/>
-      <c r="C58" s="67"/>
-      <c r="D58" s="66"/>
-      <c r="E58" s="67"/>
-      <c r="F58" s="71"/>
-      <c r="G58" s="70"/>
-      <c r="H58" s="62"/>
-      <c r="I58" s="61"/>
-      <c r="J58" s="60"/>
-      <c r="K58" s="59"/>
-      <c r="L58" s="59"/>
-      <c r="M58" s="69"/>
-      <c r="N58" s="57"/>
-      <c r="O58" s="57"/>
-      <c r="P58" s="56"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="23"/>
+      <c r="I58" s="22"/>
+      <c r="J58" s="21"/>
+      <c r="K58" s="20"/>
+      <c r="L58" s="20"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="18"/>
+      <c r="O58" s="18"/>
+      <c r="P58" s="17"/>
     </row>
     <row r="59" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="68"/>
-      <c r="C59" s="67"/>
-      <c r="D59" s="66"/>
-      <c r="E59" s="67"/>
-      <c r="F59" s="71"/>
-      <c r="G59" s="70"/>
-      <c r="H59" s="62"/>
-      <c r="I59" s="61"/>
-      <c r="J59" s="60"/>
-      <c r="K59" s="59"/>
-      <c r="L59" s="59"/>
-      <c r="M59" s="69"/>
-      <c r="N59" s="57"/>
-      <c r="O59" s="57"/>
-      <c r="P59" s="56"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="31"/>
+      <c r="H59" s="23"/>
+      <c r="I59" s="22"/>
+      <c r="J59" s="21"/>
+      <c r="K59" s="20"/>
+      <c r="L59" s="20"/>
+      <c r="M59" s="30"/>
+      <c r="N59" s="18"/>
+      <c r="O59" s="18"/>
+      <c r="P59" s="17"/>
     </row>
     <row r="60" spans="2:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="68"/>
-      <c r="C60" s="67"/>
-      <c r="D60" s="66"/>
-      <c r="E60" s="65"/>
-      <c r="F60" s="64"/>
-      <c r="G60" s="63"/>
-      <c r="H60" s="62"/>
-      <c r="I60" s="61"/>
-      <c r="J60" s="60"/>
-      <c r="K60" s="59"/>
-      <c r="L60" s="59"/>
-      <c r="M60" s="58"/>
-      <c r="N60" s="57"/>
-      <c r="O60" s="57"/>
-      <c r="P60" s="56"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="23"/>
+      <c r="I60" s="22"/>
+      <c r="J60" s="21"/>
+      <c r="K60" s="20"/>
+      <c r="L60" s="20"/>
+      <c r="M60" s="19"/>
+      <c r="N60" s="18"/>
+      <c r="O60" s="18"/>
+      <c r="P60" s="17"/>
     </row>
     <row r="61" spans="2:16" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="55"/>
-      <c r="C61" s="54"/>
-      <c r="D61" s="54"/>
-      <c r="E61" s="54"/>
-      <c r="F61" s="54"/>
-      <c r="G61" s="54"/>
-      <c r="H61" s="53">
-        <f>SUM(H51:H60)</f>
+      <c r="B61" s="16"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="14">
+        <f t="shared" ref="H61:O61" si="0">SUM(H51:H60)</f>
         <v>0</v>
       </c>
-      <c r="I61" s="53">
-        <f>SUM(I51:I60)</f>
+      <c r="I61" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J61" s="52">
-        <f>SUM(J51:J60)</f>
+      <c r="J61" s="13">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K61" s="51">
-        <f>SUM(K51:K60)</f>
+      <c r="K61" s="12">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L61" s="51">
-        <f>SUM(L51:L60)</f>
+      <c r="L61" s="12">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M61" s="51">
-        <f>SUM(M51:M60)</f>
+      <c r="M61" s="12">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N61" s="51">
-        <f>SUM(N51:N60)</f>
+      <c r="N61" s="12">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O61" s="51">
-        <f>SUM(O51:O60)</f>
+      <c r="O61" s="12">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P61" s="50">
+      <c r="P61" s="11">
         <f>SUM(P51:Q60)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="2:16" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="49" t="s">
+      <c r="B62" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C62" s="48"/>
-      <c r="D62" s="48"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="47"/>
-      <c r="H62" s="47"/>
-      <c r="I62" s="47"/>
-      <c r="J62" s="46"/>
-      <c r="K62" s="46"/>
-      <c r="L62" s="45" t="s">
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+      <c r="L62" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="M62" s="44"/>
-      <c r="N62" s="43"/>
-      <c r="O62" s="42"/>
-      <c r="P62" s="41"/>
+      <c r="M62" s="122"/>
+      <c r="N62" s="123"/>
+      <c r="O62" s="124"/>
+      <c r="P62" s="125"/>
     </row>
     <row r="63" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="40"/>
-      <c r="C63" s="39"/>
-      <c r="D63" s="39"/>
-      <c r="E63" s="39"/>
-      <c r="F63" s="39"/>
-      <c r="G63" s="39"/>
-      <c r="H63" s="39"/>
-      <c r="I63" s="38"/>
-      <c r="L63" s="37" t="s">
+      <c r="B63" s="6"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="4"/>
+      <c r="L63" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="M63" s="37"/>
-      <c r="N63" s="37"/>
-      <c r="O63" s="36"/>
-      <c r="P63" s="35"/>
+      <c r="M63" s="126"/>
+      <c r="N63" s="126"/>
+      <c r="O63" s="127"/>
+      <c r="P63" s="128"/>
     </row>
     <row r="64" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="32"/>
-      <c r="C64" s="32"/>
-      <c r="D64" s="32"/>
-      <c r="E64" s="32"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="32"/>
-      <c r="I64" s="32"/>
-      <c r="J64" s="32"/>
-      <c r="K64" s="34"/>
-      <c r="L64" s="33" t="s">
+      <c r="B64" s="131"/>
+      <c r="C64" s="131"/>
+      <c r="D64" s="131"/>
+      <c r="E64" s="131"/>
+      <c r="F64" s="131"/>
+      <c r="G64" s="131"/>
+      <c r="H64" s="131"/>
+      <c r="I64" s="131"/>
+      <c r="J64" s="131"/>
+      <c r="K64" s="132"/>
+      <c r="L64" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="M64" s="33"/>
-      <c r="N64" s="33"/>
-      <c r="O64" s="9"/>
-      <c r="P64" s="8"/>
+      <c r="M64" s="133"/>
+      <c r="N64" s="133"/>
+      <c r="O64" s="134"/>
+      <c r="P64" s="135"/>
     </row>
     <row r="65" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="32"/>
-      <c r="C65" s="32"/>
-      <c r="D65" s="32"/>
-      <c r="E65" s="32"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="32"/>
-      <c r="I65" s="32"/>
-      <c r="J65" s="32"/>
-      <c r="L65" s="31" t="s">
+      <c r="B65" s="131"/>
+      <c r="C65" s="131"/>
+      <c r="D65" s="131"/>
+      <c r="E65" s="131"/>
+      <c r="F65" s="131"/>
+      <c r="G65" s="131"/>
+      <c r="H65" s="131"/>
+      <c r="I65" s="131"/>
+      <c r="J65" s="131"/>
+      <c r="L65" s="136" t="s">
         <v>4</v>
       </c>
-      <c r="M65" s="30"/>
-      <c r="N65" s="29"/>
-      <c r="O65" s="28"/>
-      <c r="P65" s="27"/>
+      <c r="M65" s="137"/>
+      <c r="N65" s="138"/>
+      <c r="O65" s="139"/>
+      <c r="P65" s="140"/>
     </row>
     <row r="66" spans="2:16" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="26"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
-      <c r="I66" s="25"/>
-      <c r="J66" s="25"/>
-      <c r="L66" s="24" t="s">
+      <c r="B66" s="149"/>
+      <c r="C66" s="150"/>
+      <c r="D66" s="150"/>
+      <c r="E66" s="150"/>
+      <c r="F66" s="150"/>
+      <c r="G66" s="150"/>
+      <c r="H66" s="150"/>
+      <c r="I66" s="150"/>
+      <c r="J66" s="150"/>
+      <c r="L66" s="151" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="23"/>
-      <c r="N66" s="22"/>
-      <c r="O66" s="21"/>
-      <c r="P66" s="20"/>
+      <c r="M66" s="152"/>
+      <c r="N66" s="153"/>
+      <c r="O66" s="154"/>
+      <c r="P66" s="155"/>
     </row>
     <row r="67" spans="2:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="19"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="19"/>
-      <c r="E67" s="19"/>
-      <c r="F67" s="19"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="19"/>
-      <c r="I67" s="19"/>
-      <c r="J67" s="19"/>
-      <c r="L67" s="18" t="s">
+      <c r="B67" s="156"/>
+      <c r="C67" s="156"/>
+      <c r="D67" s="156"/>
+      <c r="E67" s="156"/>
+      <c r="F67" s="156"/>
+      <c r="G67" s="156"/>
+      <c r="H67" s="156"/>
+      <c r="I67" s="156"/>
+      <c r="J67" s="156"/>
+      <c r="L67" s="157" t="s">
         <v>2</v>
       </c>
-      <c r="M67" s="17"/>
-      <c r="N67" s="16"/>
-      <c r="O67" s="15"/>
-      <c r="P67" s="14"/>
+      <c r="M67" s="158"/>
+      <c r="N67" s="159"/>
+      <c r="O67" s="129"/>
+      <c r="P67" s="130"/>
     </row>
     <row r="68" spans="2:16" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="13"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="L68" s="12" t="s">
+      <c r="B68" s="3"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="L68" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="M68" s="11"/>
-      <c r="N68" s="10"/>
-      <c r="O68" s="9"/>
-      <c r="P68" s="8"/>
+      <c r="M68" s="142"/>
+      <c r="N68" s="143"/>
+      <c r="O68" s="134"/>
+      <c r="P68" s="135"/>
     </row>
     <row r="69" spans="2:16" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="L69" s="6" t="s">
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="L69" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="M69" s="5"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="3"/>
-      <c r="P69" s="2"/>
+      <c r="M69" s="145"/>
+      <c r="N69" s="146"/>
+      <c r="O69" s="147"/>
+      <c r="P69" s="148"/>
     </row>
     <row r="70" spans="2:16" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="75">
-    <mergeCell ref="A4:Q4"/>
-    <mergeCell ref="A5:Q5"/>
-    <mergeCell ref="A6:Q6"/>
-    <mergeCell ref="A7:Q7"/>
-    <mergeCell ref="A8:Q8"/>
-    <mergeCell ref="A11:Q11"/>
-    <mergeCell ref="A12:Q12"/>
-    <mergeCell ref="A13:Q13"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:I15"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="L68:N68"/>
+    <mergeCell ref="O68:P68"/>
+    <mergeCell ref="L69:N69"/>
+    <mergeCell ref="O69:P69"/>
+    <mergeCell ref="B66:J66"/>
+    <mergeCell ref="L66:N66"/>
+    <mergeCell ref="O66:P66"/>
+    <mergeCell ref="B67:J67"/>
+    <mergeCell ref="L67:N67"/>
+    <mergeCell ref="L63:N63"/>
+    <mergeCell ref="O63:P63"/>
+    <mergeCell ref="O67:P67"/>
+    <mergeCell ref="B64:K64"/>
+    <mergeCell ref="L64:N64"/>
+    <mergeCell ref="O64:P64"/>
+    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="L65:N65"/>
+    <mergeCell ref="O65:P65"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A47:Q47"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="L62:N62"/>
+    <mergeCell ref="O62:P62"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="E20:I20"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="N21:P21"/>
     <mergeCell ref="B16:D19"/>
     <mergeCell ref="E16:I16"/>
     <mergeCell ref="J16:M16"/>
@@ -4234,56 +4070,18 @@
     <mergeCell ref="E19:I19"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="N19:P19"/>
-    <mergeCell ref="E20:I20"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="A42:Q42"/>
-    <mergeCell ref="A47:Q47"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="L62:N62"/>
-    <mergeCell ref="O62:P62"/>
-    <mergeCell ref="L63:N63"/>
-    <mergeCell ref="O63:P63"/>
-    <mergeCell ref="O67:P67"/>
-    <mergeCell ref="B64:K64"/>
-    <mergeCell ref="L64:N64"/>
-    <mergeCell ref="O64:P64"/>
-    <mergeCell ref="B65:J65"/>
-    <mergeCell ref="L65:N65"/>
-    <mergeCell ref="O65:P65"/>
-    <mergeCell ref="L68:N68"/>
-    <mergeCell ref="O68:P68"/>
-    <mergeCell ref="L69:N69"/>
-    <mergeCell ref="O69:P69"/>
-    <mergeCell ref="B66:J66"/>
-    <mergeCell ref="L66:N66"/>
-    <mergeCell ref="O66:P66"/>
-    <mergeCell ref="B67:J67"/>
-    <mergeCell ref="L67:N67"/>
+    <mergeCell ref="A11:Q11"/>
+    <mergeCell ref="A12:Q12"/>
+    <mergeCell ref="A13:Q13"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A5:Q5"/>
+    <mergeCell ref="A6:Q6"/>
+    <mergeCell ref="A7:Q7"/>
+    <mergeCell ref="A8:Q8"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.35433070866141736" right="0.35433070866141736" top="0.98425196850393704" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
